--- a/Sensitivity_PSNR_Starfish.xlsx
+++ b/Sensitivity_PSNR_Starfish.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B998B313-79FC-435F-911A-78251B3229C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8674BF06-9CB1-40D0-B404-2152FCCD629C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CC9B4AF2-536C-4C75-9031-066FCFFFC11E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BA8D9B99-8199-4B84-BAE0-0F394C5EB400}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -442,7 +445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45EDD026-2871-4B98-8B19-314F05C71F8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A2DFDD8-6C70-4953-BBF2-432BE9683FE0}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -576,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB38273D-E0D1-4B23-A4B5-D1D084D55084}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E53BD21E-86D6-40AE-AD9E-2BE839B1B109}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -585,7 +588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0506629A-652C-42C0-A2F7-8509DECF9C88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BE1C653-5FF8-4693-8236-57B166C24286}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
